--- a/Excel/Delivery.xlsx
+++ b/Excel/Delivery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Documents\UW\4_semester\CPP\ccp_in_QF_II_project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C83D61-7884-4F9B-8A93-A9E11BF97FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A6F928-DEE7-447F-987A-F4D51E9BE809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04710B95-6077-4540-8D71-F796DBE07594}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{04710B95-6077-4540-8D71-F796DBE07594}"/>
   </bookViews>
   <sheets>
     <sheet name="Fly Params" sheetId="4" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>S0</t>
   </si>
@@ -98,14 +98,14 @@
   <si>
     <t>d</t>
   </si>
-  <si>
-    <t>&lt;- alreay in the pricer</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -273,11 +273,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -287,7 +287,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,10 +417,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Price vs spot'!$A$2:$A$73</c:f>
+              <c:f>'Price vs spot'!$A$2:$A$70</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>64</c:v>
                 </c:pt>
@@ -630,207 +630,207 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Price vs spot'!$B$2:$B$73</c:f>
+              <c:f>'Price vs spot'!$B$2:$B$70</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
-                  <c:v>5.7802762127323604E-4</c:v>
+                  <c:v>3.3781609313720651E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2921978104407685E-3</c:v>
+                  <c:v>3.8591942079214903E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0759413245239102E-2</c:v>
+                  <c:v>4.4261351152904638E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.7672814221967315E-2</c:v>
+                  <c:v>5.1234132061416915E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.7053968619874524E-2</c:v>
+                  <c:v>6.0333581098092282E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.9206575261829357E-2</c:v>
+                  <c:v>7.1435251667494981E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.3847362830929058E-2</c:v>
+                  <c:v>8.4595596259880779E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.1024789789198906E-2</c:v>
+                  <c:v>0.10011887635604211</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.1666128714429362E-2</c:v>
+                  <c:v>0.11919938686421716</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1154243465752316</c:v>
+                  <c:v>0.14189379946324721</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.14324026094108433</c:v>
+                  <c:v>0.16831151824210622</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.17508550227127273</c:v>
+                  <c:v>0.19814084577517121</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.21169323732355849</c:v>
+                  <c:v>0.23091988251853479</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.25321304445905923</c:v>
+                  <c:v>0.26765751555109318</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.29884518042050701</c:v>
+                  <c:v>0.30887950831888134</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3476308199326823</c:v>
+                  <c:v>0.35407744390047924</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.40003446385009056</c:v>
+                  <c:v>0.40250723768647845</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.45614602680065275</c:v>
+                  <c:v>0.45512610000140086</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.51590727456836305</c:v>
+                  <c:v>0.51187053532503768</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.58173984775571341</c:v>
+                  <c:v>0.5713674303370766</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.65216735892656885</c:v>
+                  <c:v>0.63558377549095724</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7222954642128343</c:v>
+                  <c:v>0.70411524330353359</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.7942621544213111</c:v>
+                  <c:v>0.77504782060320565</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8696561546205146</c:v>
+                  <c:v>0.8478611097265123</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.94881954696997894</c:v>
+                  <c:v>0.92308148099237286</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.0257637257324177</c:v>
+                  <c:v>0.99883754700426053</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.1059680218304386</c:v>
+                  <c:v>1.0736306956031534</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.1876111685017818</c:v>
+                  <c:v>1.1488785771719279</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.2672404148710861</c:v>
+                  <c:v>1.2237400012648685</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.3466312891349901</c:v>
+                  <c:v>1.3002643783226162</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.4233522680496087</c:v>
+                  <c:v>1.3751683748167274</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.4974060105905203</c:v>
+                  <c:v>1.4463271767432175</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.5657448605290369</c:v>
+                  <c:v>1.5113805166605587</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.6337333794203239</c:v>
+                  <c:v>1.5719749376172523</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.6940851574876952</c:v>
+                  <c:v>1.6284146205168817</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.7485611302622033</c:v>
+                  <c:v>1.679166016859952</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.7961272222374376</c:v>
+                  <c:v>1.724443726409941</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.8337855636355691</c:v>
+                  <c:v>1.7619997277092896</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.8623606450437009</c:v>
+                  <c:v>1.7944294557539386</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.8896368477748275</c:v>
+                  <c:v>1.8228871862030385</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.9109108460443416</c:v>
+                  <c:v>1.8440028679582952</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.9273668560335011</c:v>
+                  <c:v>1.8541485398410487</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.9327622287392199</c:v>
+                  <c:v>1.8595770353637633</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.9237530862459042</c:v>
+                  <c:v>1.8546527873193597</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.9194977280920931</c:v>
+                  <c:v>1.8385378948185132</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.8875984162816088</c:v>
+                  <c:v>1.8150871715488197</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.8583570568708385</c:v>
+                  <c:v>1.7842187977521906</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.8209022236268915</c:v>
+                  <c:v>1.748944861603503</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.7813826357425144</c:v>
+                  <c:v>1.7061606039693604</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.7262994092417063</c:v>
+                  <c:v>1.6491734487326131</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.6533599565203136</c:v>
+                  <c:v>1.5875823895504331</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.5769372685193614</c:v>
+                  <c:v>1.5160433851190147</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.4995369072041882</c:v>
+                  <c:v>1.4364705569715133</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.4255853549065023</c:v>
+                  <c:v>1.3514644621167671</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.3255171062113398</c:v>
+                  <c:v>1.2682833482919555</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.2283043623867513</c:v>
+                  <c:v>1.1776195316424438</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.1245993325806851</c:v>
+                  <c:v>1.0794967054167812</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.0178976499963861</c:v>
+                  <c:v>0.97809732338754474</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.9166362797813461</c:v>
+                  <c:v>0.86849204494400922</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.81117603483658973</c:v>
+                  <c:v>0.75619553501110337</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.7060296572332434</c:v>
+                  <c:v>0.65417822699185058</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.61224827405471438</c:v>
+                  <c:v>0.54052392455341369</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.49413608286002786</c:v>
+                  <c:v>0.43968912433395713</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.35574065961323886</c:v>
+                  <c:v>0.33951651215931578</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.23850126552222406</c:v>
+                  <c:v>0.22463025352351285</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.11931414396467954</c:v>
+                  <c:v>0.11314472277012083</c:v>
                 </c:pt>
                 <c:pt idx="66">
                   <c:v>0</c:v>
@@ -932,7 +932,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1075,7 +1075,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1113,10 +1113,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Price vs barrier'!$A$2:$A$42</c:f>
+              <c:f>'Price vs barrier'!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>90</c:v>
                 </c:pt>
@@ -1245,10 +1245,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Price vs barrier'!$B$2:$B$42</c:f>
+              <c:f>'Price vs barrier'!$B$2:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1313,64 +1313,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.7962691171640186E-2</c:v>
+                  <c:v>3.2715266890966266E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.7777492243128901E-2</c:v>
+                  <c:v>8.5008784462401454E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.14543881139606851</c:v>
+                  <c:v>0.15062073901751249</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.23904628048718468</c:v>
+                  <c:v>0.19761554699401707</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.30659956296545854</c:v>
+                  <c:v>0.28632755292985834</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.40888188953313342</c:v>
+                  <c:v>0.37961928114562227</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.52739383298460396</c:v>
+                  <c:v>0.48552236378629043</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.64381212836634294</c:v>
+                  <c:v>0.61975345060986164</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.77595610507325929</c:v>
+                  <c:v>0.74300271195763656</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.91102014561373323</c:v>
+                  <c:v>0.86987482262286164</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.0374245671186078</c:v>
+                  <c:v>0.99432704623960966</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.1719679818243085</c:v>
+                  <c:v>1.1062289920781687</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.2804156906125748</c:v>
+                  <c:v>1.2216488451997378</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.3854052142857753</c:v>
+                  <c:v>1.3323159912990032</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.4883406698727892</c:v>
+                  <c:v>1.4352010028062399</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.5903674327693906</c:v>
+                  <c:v>1.5236078466212977</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.6789952010944873</c:v>
+                  <c:v>1.6063523043173316</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.7462334310187764</c:v>
+                  <c:v>1.6765523294840019</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.8043124292199</c:v>
+                  <c:v>1.7333905947399479</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.8583570568708385</c:v>
+                  <c:v>1.7842187977521906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1655,10 +1655,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Price vs vol'!$A$2:$A$42</c:f>
+              <c:f>'Price vs vol'!$A$2:$A$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
                   <c:v>0.1</c:v>
                 </c:pt>
@@ -1787,132 +1787,132 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Price vs vol'!$B$2:$B$42</c:f>
+              <c:f>'Price vs vol'!$B$2:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="41"/>
+                <c:ptCount val="42"/>
                 <c:pt idx="0">
-                  <c:v>4.2445489795389708</c:v>
+                  <c:v>4.1913717983835088</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.9688435128858908</c:v>
+                  <c:v>3.9125836781529522</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7192454920194908</c:v>
+                  <c:v>3.6593723710410586</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.4912475960139853</c:v>
+                  <c:v>3.4275314445771778</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2802441249134953</c:v>
+                  <c:v>3.2121047249499206</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.0833213713433389</c:v>
+                  <c:v>3.0121315878495549</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.8982338587863437</c:v>
+                  <c:v>2.8268647789696582</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.7241566692795551</c:v>
+                  <c:v>2.6521054667032491</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.5636423386376928</c:v>
+                  <c:v>2.4879074618227905</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.4050048511597044</c:v>
+                  <c:v>2.3330734883356836</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.2605169715067799</c:v>
+                  <c:v>2.1844945065091466</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.1218130343404926</c:v>
+                  <c:v>2.0436406444439843</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9806582646617201</c:v>
+                  <c:v>1.9104214044523147</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.8583570568708385</c:v>
+                  <c:v>1.7842187977521906</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.7423928408351603</c:v>
+                  <c:v>1.6677598548520081</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.63389471493233</c:v>
+                  <c:v>1.5610886272180231</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.5383738961462861</c:v>
+                  <c:v>1.4610674349610786</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4455746876770448</c:v>
+                  <c:v>1.3638243572321311</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.3527977916074612</c:v>
+                  <c:v>1.2710642558820329</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.2645245399924967</c:v>
+                  <c:v>1.1854764273945904</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1777505209969146</c:v>
+                  <c:v>1.1091705204489983</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.0977296836683994</c:v>
+                  <c:v>1.03752926171369</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0235488612128414</c:v>
+                  <c:v>0.96733522089546753</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.95668597429344437</c:v>
+                  <c:v>0.89997568264630168</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.89632615681331451</c:v>
+                  <c:v>0.8383096665903782</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.84301463188661074</c:v>
+                  <c:v>0.78050128828524201</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.79858109091482099</c:v>
+                  <c:v>0.72565606895011037</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.75757774569119007</c:v>
+                  <c:v>0.67467062358963226</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.71314214652871044</c:v>
+                  <c:v>0.63146428369368657</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.66480853261455408</c:v>
+                  <c:v>0.59363613112031643</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.61607079502593898</c:v>
+                  <c:v>0.5599062172089031</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.57285369430810995</c:v>
+                  <c:v>0.52806381781686795</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.53927077101698728</c:v>
+                  <c:v>0.49608300301630237</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.51328378740108604</c:v>
+                  <c:v>0.46471500553838929</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.48979766948023062</c:v>
+                  <c:v>0.43590460968661482</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.46582670898617451</c:v>
+                  <c:v>0.41005844020134674</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.44074211989477519</c:v>
+                  <c:v>0.38719189312834423</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.41404347041275891</c:v>
+                  <c:v>0.36704488626576648</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.38512183991061377</c:v>
+                  <c:v>0.34929810662353233</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.35582019392578701</c:v>
+                  <c:v>0.33290923233184699</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.32770480078904463</c:v>
+                  <c:v>0.31688311309744677</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4215,95 +4215,83 @@
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="1">
         <v>110</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>0.23</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="1">
         <v>130</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="1">
         <v>0.5</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="1">
         <v>100</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="1">
         <v>110</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="1">
         <v>120</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="1">
         <v>0.05</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>0</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="10"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4318,7 +4306,9 @@
   <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -4333,602 +4323,602 @@
       <c r="A2" s="1">
         <v>64</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.PriceButterfly(A2,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>5.7802762127323604E-4</v>
+      <c r="B2" s="14" cm="1">
+        <f t="array" ref="B2">_xll.PriceButterfly(A2,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.3781609313720651E-2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>65</v>
       </c>
-      <c r="B3" s="1" cm="1">
-        <f t="array" ref="B3">_xll.PriceButterfly(A3,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>5.2921978104407685E-3</v>
+      <c r="B3" s="14" cm="1">
+        <f t="array" ref="B3">_xll.PriceButterfly(A3,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.8591942079214903E-2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>66</v>
       </c>
-      <c r="B4" s="1" cm="1">
-        <f t="array" ref="B4">_xll.PriceButterfly(A4,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.0759413245239102E-2</v>
+      <c r="B4" s="14" cm="1">
+        <f t="array" ref="B4">_xll.PriceButterfly(A4,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>4.4261351152904638E-2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>67</v>
       </c>
-      <c r="B5" s="1" cm="1">
-        <f t="array" ref="B5">_xll.PriceButterfly(A5,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7672814221967315E-2</v>
+      <c r="B5" s="14" cm="1">
+        <f t="array" ref="B5">_xll.PriceButterfly(A5,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>5.1234132061416915E-2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>68</v>
       </c>
-      <c r="B6" s="1" cm="1">
-        <f t="array" ref="B6">_xll.PriceButterfly(A6,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.7053968619874524E-2</v>
+      <c r="B6" s="14" cm="1">
+        <f t="array" ref="B6">_xll.PriceButterfly(A6,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>6.0333581098092282E-2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>69</v>
       </c>
-      <c r="B7" s="1" cm="1">
-        <f t="array" ref="B7">_xll.PriceButterfly(A7,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.9206575261829357E-2</v>
+      <c r="B7" s="14" cm="1">
+        <f t="array" ref="B7">_xll.PriceButterfly(A7,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>7.1435251667494981E-2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>70</v>
       </c>
-      <c r="B8" s="1" cm="1">
-        <f t="array" ref="B8">_xll.PriceButterfly(A8,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>5.3847362830929058E-2</v>
+      <c r="B8" s="14" cm="1">
+        <f t="array" ref="B8">_xll.PriceButterfly(A8,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>8.4595596259880779E-2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>71</v>
       </c>
-      <c r="B9" s="1" cm="1">
-        <f t="array" ref="B9">_xll.PriceButterfly(A9,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>7.1024789789198906E-2</v>
+      <c r="B9" s="14" cm="1">
+        <f t="array" ref="B9">_xll.PriceButterfly(A9,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.10011887635604211</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>72</v>
       </c>
-      <c r="B10" s="1" cm="1">
-        <f t="array" ref="B10">_xll.PriceButterfly(A10,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>9.1666128714429362E-2</v>
+      <c r="B10" s="14" cm="1">
+        <f t="array" ref="B10">_xll.PriceButterfly(A10,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.11919938686421716</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>73</v>
       </c>
-      <c r="B11" s="1" cm="1">
-        <f t="array" ref="B11">_xll.PriceButterfly(A11,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.1154243465752316</v>
+      <c r="B11" s="14" cm="1">
+        <f t="array" ref="B11">_xll.PriceButterfly(A11,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.14189379946324721</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>74</v>
       </c>
-      <c r="B12" s="1" cm="1">
-        <f t="array" ref="B12">_xll.PriceButterfly(A12,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.14324026094108433</v>
+      <c r="B12" s="14" cm="1">
+        <f t="array" ref="B12">_xll.PriceButterfly(A12,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.16831151824210622</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>75</v>
       </c>
-      <c r="B13" s="1" cm="1">
-        <f t="array" ref="B13">_xll.PriceButterfly(A13,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.17508550227127273</v>
+      <c r="B13" s="14" cm="1">
+        <f t="array" ref="B13">_xll.PriceButterfly(A13,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.19814084577517121</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>76</v>
       </c>
-      <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xll.PriceButterfly(A14,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.21169323732355849</v>
+      <c r="B14" s="14" cm="1">
+        <f t="array" ref="B14">_xll.PriceButterfly(A14,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.23091988251853479</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>77</v>
       </c>
-      <c r="B15" s="1" cm="1">
-        <f t="array" ref="B15">_xll.PriceButterfly(A15,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.25321304445905923</v>
+      <c r="B15" s="14" cm="1">
+        <f t="array" ref="B15">_xll.PriceButterfly(A15,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.26765751555109318</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>78</v>
       </c>
-      <c r="B16" s="1" cm="1">
-        <f t="array" ref="B16">_xll.PriceButterfly(A16,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.29884518042050701</v>
+      <c r="B16" s="14" cm="1">
+        <f t="array" ref="B16">_xll.PriceButterfly(A16,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.30887950831888134</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>79</v>
       </c>
-      <c r="B17" s="1" cm="1">
-        <f t="array" ref="B17">_xll.PriceButterfly(A17,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.3476308199326823</v>
+      <c r="B17" s="14" cm="1">
+        <f t="array" ref="B17">_xll.PriceButterfly(A17,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.35407744390047924</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>80</v>
       </c>
-      <c r="B18" s="1" cm="1">
-        <f t="array" ref="B18">_xll.PriceButterfly(A18,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.40003446385009056</v>
+      <c r="B18" s="14" cm="1">
+        <f t="array" ref="B18">_xll.PriceButterfly(A18,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.40250723768647845</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>81</v>
       </c>
-      <c r="B19" s="1" cm="1">
-        <f t="array" ref="B19">_xll.PriceButterfly(A19,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.45614602680065275</v>
+      <c r="B19" s="14" cm="1">
+        <f t="array" ref="B19">_xll.PriceButterfly(A19,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.45512610000140086</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>82</v>
       </c>
-      <c r="B20" s="1" cm="1">
-        <f t="array" ref="B20">_xll.PriceButterfly(A20,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.51590727456836305</v>
+      <c r="B20" s="14" cm="1">
+        <f t="array" ref="B20">_xll.PriceButterfly(A20,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.51187053532503768</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>83</v>
       </c>
-      <c r="B21" s="1" cm="1">
-        <f t="array" ref="B21">_xll.PriceButterfly(A21,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.58173984775571341</v>
+      <c r="B21" s="14" cm="1">
+        <f t="array" ref="B21">_xll.PriceButterfly(A21,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.5713674303370766</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>84</v>
       </c>
-      <c r="B22" s="1" cm="1">
-        <f t="array" ref="B22">_xll.PriceButterfly(A22,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.65216735892656885</v>
+      <c r="B22" s="14" cm="1">
+        <f t="array" ref="B22">_xll.PriceButterfly(A22,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.63558377549095724</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>85</v>
       </c>
-      <c r="B23" s="1" cm="1">
-        <f t="array" ref="B23">_xll.PriceButterfly(A23,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.7222954642128343</v>
+      <c r="B23" s="14" cm="1">
+        <f t="array" ref="B23">_xll.PriceButterfly(A23,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.70411524330353359</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>86</v>
       </c>
-      <c r="B24" s="1" cm="1">
-        <f t="array" ref="B24">_xll.PriceButterfly(A24,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.7942621544213111</v>
+      <c r="B24" s="14" cm="1">
+        <f t="array" ref="B24">_xll.PriceButterfly(A24,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.77504782060320565</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>87</v>
       </c>
-      <c r="B25" s="1" cm="1">
-        <f t="array" ref="B25">_xll.PriceButterfly(A25,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.8696561546205146</v>
+      <c r="B25" s="14" cm="1">
+        <f t="array" ref="B25">_xll.PriceButterfly(A25,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.8478611097265123</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>88</v>
       </c>
-      <c r="B26" s="1" cm="1">
-        <f t="array" ref="B26">_xll.PriceButterfly(A26,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.94881954696997894</v>
+      <c r="B26" s="14" cm="1">
+        <f t="array" ref="B26">_xll.PriceButterfly(A26,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.92308148099237286</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>89</v>
       </c>
-      <c r="B27" s="1" cm="1">
-        <f t="array" ref="B27">_xll.PriceButterfly(A27,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.0257637257324177</v>
+      <c r="B27" s="14" cm="1">
+        <f t="array" ref="B27">_xll.PriceButterfly(A27,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.99883754700426053</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>90</v>
       </c>
-      <c r="B28" s="1" cm="1">
-        <f t="array" ref="B28">_xll.PriceButterfly(A28,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.1059680218304386</v>
+      <c r="B28" s="14" cm="1">
+        <f t="array" ref="B28">_xll.PriceButterfly(A28,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.0736306956031534</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>91</v>
       </c>
-      <c r="B29" s="1" cm="1">
-        <f t="array" ref="B29">_xll.PriceButterfly(A29,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.1876111685017818</v>
+      <c r="B29" s="14" cm="1">
+        <f t="array" ref="B29">_xll.PriceButterfly(A29,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.1488785771719279</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>92</v>
       </c>
-      <c r="B30" s="1" cm="1">
-        <f t="array" ref="B30">_xll.PriceButterfly(A30,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.2672404148710861</v>
+      <c r="B30" s="14" cm="1">
+        <f t="array" ref="B30">_xll.PriceButterfly(A30,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.2237400012648685</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>93</v>
       </c>
-      <c r="B31" s="1" cm="1">
-        <f t="array" ref="B31">_xll.PriceButterfly(A31,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.3466312891349901</v>
+      <c r="B31" s="14" cm="1">
+        <f t="array" ref="B31">_xll.PriceButterfly(A31,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.3002643783226162</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>94</v>
       </c>
-      <c r="B32" s="1" cm="1">
-        <f t="array" ref="B32">_xll.PriceButterfly(A32,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.4233522680496087</v>
+      <c r="B32" s="14" cm="1">
+        <f t="array" ref="B32">_xll.PriceButterfly(A32,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.3751683748167274</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>95</v>
       </c>
-      <c r="B33" s="1" cm="1">
-        <f t="array" ref="B33">_xll.PriceButterfly(A33,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.4974060105905203</v>
+      <c r="B33" s="14" cm="1">
+        <f t="array" ref="B33">_xll.PriceButterfly(A33,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.4463271767432175</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>96</v>
       </c>
-      <c r="B34" s="1" cm="1">
-        <f t="array" ref="B34">_xll.PriceButterfly(A34,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.5657448605290369</v>
+      <c r="B34" s="14" cm="1">
+        <f t="array" ref="B34">_xll.PriceButterfly(A34,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5113805166605587</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>97</v>
       </c>
-      <c r="B35" s="1" cm="1">
-        <f t="array" ref="B35">_xll.PriceButterfly(A35,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.6337333794203239</v>
+      <c r="B35" s="14" cm="1">
+        <f t="array" ref="B35">_xll.PriceButterfly(A35,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5719749376172523</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>98</v>
       </c>
-      <c r="B36" s="1" cm="1">
-        <f t="array" ref="B36">_xll.PriceButterfly(A36,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.6940851574876952</v>
+      <c r="B36" s="14" cm="1">
+        <f t="array" ref="B36">_xll.PriceButterfly(A36,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.6284146205168817</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>99</v>
       </c>
-      <c r="B37" s="1" cm="1">
-        <f t="array" ref="B37">_xll.PriceButterfly(A37,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7485611302622033</v>
+      <c r="B37" s="14" cm="1">
+        <f t="array" ref="B37">_xll.PriceButterfly(A37,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.679166016859952</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>100</v>
       </c>
-      <c r="B38" s="1" cm="1">
-        <f t="array" ref="B38">_xll.PriceButterfly(A38,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7961272222374376</v>
+      <c r="B38" s="14" cm="1">
+        <f t="array" ref="B38">_xll.PriceButterfly(A38,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.724443726409941</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>101</v>
       </c>
-      <c r="B39" s="1" cm="1">
-        <f t="array" ref="B39">_xll.PriceButterfly(A39,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8337855636355691</v>
+      <c r="B39" s="14" cm="1">
+        <f t="array" ref="B39">_xll.PriceButterfly(A39,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7619997277092896</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>102</v>
       </c>
-      <c r="B40" s="1" cm="1">
-        <f t="array" ref="B40">_xll.PriceButterfly(A40,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8623606450437009</v>
+      <c r="B40" s="14" cm="1">
+        <f t="array" ref="B40">_xll.PriceButterfly(A40,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7944294557539386</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>103</v>
       </c>
-      <c r="B41" s="1" cm="1">
-        <f t="array" ref="B41">_xll.PriceButterfly(A41,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8896368477748275</v>
+      <c r="B41" s="14" cm="1">
+        <f t="array" ref="B41">_xll.PriceButterfly(A41,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8228871862030385</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>104</v>
       </c>
-      <c r="B42" s="1" cm="1">
-        <f t="array" ref="B42">_xll.PriceButterfly(A42,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9109108460443416</v>
+      <c r="B42" s="14" cm="1">
+        <f t="array" ref="B42">_xll.PriceButterfly(A42,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8440028679582952</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>105</v>
       </c>
-      <c r="B43" s="1" cm="1">
-        <f t="array" ref="B43">_xll.PriceButterfly(A43,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9273668560335011</v>
+      <c r="B43" s="14" cm="1">
+        <f t="array" ref="B43">_xll.PriceButterfly(A43,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8541485398410487</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>106</v>
       </c>
-      <c r="B44" s="1" cm="1">
-        <f t="array" ref="B44">_xll.PriceButterfly(A44,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9327622287392199</v>
+      <c r="B44" s="14" cm="1">
+        <f t="array" ref="B44">_xll.PriceButterfly(A44,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8595770353637633</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>107</v>
       </c>
-      <c r="B45" s="1" cm="1">
-        <f t="array" ref="B45">_xll.PriceButterfly(A45,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9237530862459042</v>
+      <c r="B45" s="14" cm="1">
+        <f t="array" ref="B45">_xll.PriceButterfly(A45,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8546527873193597</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>108</v>
       </c>
-      <c r="B46" s="1" cm="1">
-        <f t="array" ref="B46">_xll.PriceButterfly(A46,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9194977280920931</v>
+      <c r="B46" s="14" cm="1">
+        <f t="array" ref="B46">_xll.PriceButterfly(A46,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8385378948185132</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>109</v>
       </c>
-      <c r="B47" s="1" cm="1">
-        <f t="array" ref="B47">_xll.PriceButterfly(A47,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8875984162816088</v>
+      <c r="B47" s="14" cm="1">
+        <f t="array" ref="B47">_xll.PriceButterfly(A47,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.8150871715488197</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>110</v>
       </c>
-      <c r="B48" s="1" cm="1">
-        <f t="array" ref="B48">_xll.PriceButterfly(A48,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8583570568708385</v>
+      <c r="B48" s="14" cm="1">
+        <f t="array" ref="B48">_xll.PriceButterfly(A48,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7842187977521906</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>111</v>
       </c>
-      <c r="B49" s="1" cm="1">
-        <f t="array" ref="B49">_xll.PriceButterfly(A49,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8209022236268915</v>
+      <c r="B49" s="14" cm="1">
+        <f t="array" ref="B49">_xll.PriceButterfly(A49,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.748944861603503</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>112</v>
       </c>
-      <c r="B50" s="1" cm="1">
-        <f t="array" ref="B50">_xll.PriceButterfly(A50,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7813826357425144</v>
+      <c r="B50" s="14" cm="1">
+        <f t="array" ref="B50">_xll.PriceButterfly(A50,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7061606039693604</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>113</v>
       </c>
-      <c r="B51" s="1" cm="1">
-        <f t="array" ref="B51">_xll.PriceButterfly(A51,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7262994092417063</v>
+      <c r="B51" s="14" cm="1">
+        <f t="array" ref="B51">_xll.PriceButterfly(A51,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.6491734487326131</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>114</v>
       </c>
-      <c r="B52" s="1" cm="1">
-        <f t="array" ref="B52">_xll.PriceButterfly(A52,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.6533599565203136</v>
+      <c r="B52" s="14" cm="1">
+        <f t="array" ref="B52">_xll.PriceButterfly(A52,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5875823895504331</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>115</v>
       </c>
-      <c r="B53" s="1" cm="1">
-        <f t="array" ref="B53">_xll.PriceButterfly(A53,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.5769372685193614</v>
+      <c r="B53" s="14" cm="1">
+        <f t="array" ref="B53">_xll.PriceButterfly(A53,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5160433851190147</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>116</v>
       </c>
-      <c r="B54" s="1" cm="1">
-        <f t="array" ref="B54">_xll.PriceButterfly(A54,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.4995369072041882</v>
+      <c r="B54" s="14" cm="1">
+        <f t="array" ref="B54">_xll.PriceButterfly(A54,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.4364705569715133</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>117</v>
       </c>
-      <c r="B55" s="1" cm="1">
-        <f t="array" ref="B55">_xll.PriceButterfly(A55,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.4255853549065023</v>
+      <c r="B55" s="14" cm="1">
+        <f t="array" ref="B55">_xll.PriceButterfly(A55,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.3514644621167671</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>118</v>
       </c>
-      <c r="B56" s="1" cm="1">
-        <f t="array" ref="B56">_xll.PriceButterfly(A56,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.3255171062113398</v>
+      <c r="B56" s="14" cm="1">
+        <f t="array" ref="B56">_xll.PriceButterfly(A56,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.2682833482919555</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>119</v>
       </c>
-      <c r="B57" s="1" cm="1">
-        <f t="array" ref="B57">_xll.PriceButterfly(A57,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.2283043623867513</v>
+      <c r="B57" s="14" cm="1">
+        <f t="array" ref="B57">_xll.PriceButterfly(A57,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.1776195316424438</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>120</v>
       </c>
-      <c r="B58" s="1" cm="1">
-        <f t="array" ref="B58">_xll.PriceButterfly(A58,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.1245993325806851</v>
+      <c r="B58" s="14" cm="1">
+        <f t="array" ref="B58">_xll.PriceButterfly(A58,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.0794967054167812</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>121</v>
       </c>
-      <c r="B59" s="1" cm="1">
-        <f t="array" ref="B59">_xll.PriceButterfly(A59,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.0178976499963861</v>
+      <c r="B59" s="14" cm="1">
+        <f t="array" ref="B59">_xll.PriceButterfly(A59,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.97809732338754474</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>122</v>
       </c>
-      <c r="B60" s="1" cm="1">
-        <f t="array" ref="B60">_xll.PriceButterfly(A60,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.9166362797813461</v>
+      <c r="B60" s="14" cm="1">
+        <f t="array" ref="B60">_xll.PriceButterfly(A60,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.86849204494400922</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>123</v>
       </c>
-      <c r="B61" s="1" cm="1">
-        <f t="array" ref="B61">_xll.PriceButterfly(A61,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.81117603483658973</v>
+      <c r="B61" s="14" cm="1">
+        <f t="array" ref="B61">_xll.PriceButterfly(A61,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.75619553501110337</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>124</v>
       </c>
-      <c r="B62" s="1" cm="1">
-        <f t="array" ref="B62">_xll.PriceButterfly(A62,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.7060296572332434</v>
+      <c r="B62" s="14" cm="1">
+        <f t="array" ref="B62">_xll.PriceButterfly(A62,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.65417822699185058</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>125</v>
       </c>
-      <c r="B63" s="1" cm="1">
-        <f t="array" ref="B63">_xll.PriceButterfly(A63,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.61224827405471438</v>
+      <c r="B63" s="14" cm="1">
+        <f t="array" ref="B63">_xll.PriceButterfly(A63,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.54052392455341369</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>126</v>
       </c>
-      <c r="B64" s="1" cm="1">
-        <f t="array" ref="B64">_xll.PriceButterfly(A64,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.49413608286002786</v>
+      <c r="B64" s="14" cm="1">
+        <f t="array" ref="B64">_xll.PriceButterfly(A64,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.43968912433395713</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>127</v>
       </c>
-      <c r="B65" s="1" cm="1">
-        <f t="array" ref="B65">_xll.PriceButterfly(A65,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.35574065961323886</v>
+      <c r="B65" s="14" cm="1">
+        <f t="array" ref="B65">_xll.PriceButterfly(A65,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.33951651215931578</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>128</v>
       </c>
-      <c r="B66" s="1" cm="1">
-        <f t="array" ref="B66">_xll.PriceButterfly(A66,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.23850126552222406</v>
+      <c r="B66" s="14" cm="1">
+        <f t="array" ref="B66">_xll.PriceButterfly(A66,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.22463025352351285</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>129</v>
       </c>
-      <c r="B67" s="1" cm="1">
-        <f t="array" ref="B67">_xll.PriceButterfly(A67,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.11931414396467954</v>
+      <c r="B67" s="14" cm="1">
+        <f t="array" ref="B67">_xll.PriceButterfly(A67,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.11314472277012083</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>130</v>
       </c>
-      <c r="B68" s="1" cm="1">
-        <f t="array" ref="B68">_xll.PriceButterfly(A68,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
+      <c r="B68" s="14" cm="1">
+        <f t="array" ref="B68">_xll.PriceButterfly(A68,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4936,8 +4926,8 @@
       <c r="A69" s="1">
         <v>131</v>
       </c>
-      <c r="B69" s="1" cm="1">
-        <f t="array" ref="B69">_xll.PriceButterfly(A69,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
+      <c r="B69" s="14" cm="1">
+        <f t="array" ref="B69">_xll.PriceButterfly(A69,'Fly Params'!$B$5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4970,7 +4960,7 @@
         <v>90</v>
       </c>
       <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A2, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B2">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A2, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4979,7 +4969,7 @@
         <v>91</v>
       </c>
       <c r="B3" s="1" cm="1">
-        <f t="array" ref="B3">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A3, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B3">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A3, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4988,7 +4978,7 @@
         <v>92</v>
       </c>
       <c r="B4" s="1" cm="1">
-        <f t="array" ref="B4">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A4, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B4">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A4, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4997,7 +4987,7 @@
         <v>93</v>
       </c>
       <c r="B5" s="1" cm="1">
-        <f t="array" ref="B5">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A5, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B5">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A5, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5006,7 +4996,7 @@
         <v>94</v>
       </c>
       <c r="B6" s="1" cm="1">
-        <f t="array" ref="B6">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A6, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B6">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A6, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5015,7 +5005,7 @@
         <v>95</v>
       </c>
       <c r="B7" s="1" cm="1">
-        <f t="array" ref="B7">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A7, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B7">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A7, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5024,7 +5014,7 @@
         <v>96</v>
       </c>
       <c r="B8" s="1" cm="1">
-        <f t="array" ref="B8">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A8, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B8">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A8, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5033,7 +5023,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" cm="1">
-        <f t="array" ref="B9">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A9, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B9">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A9, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5042,7 +5032,7 @@
         <v>98</v>
       </c>
       <c r="B10" s="1" cm="1">
-        <f t="array" ref="B10">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A10, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B10">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A10, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5051,7 +5041,7 @@
         <v>99</v>
       </c>
       <c r="B11" s="1" cm="1">
-        <f t="array" ref="B11">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A11, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B11">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A11, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5060,7 +5050,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" cm="1">
-        <f t="array" ref="B12">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A12, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B12">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A12, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5069,7 +5059,7 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" cm="1">
-        <f t="array" ref="B13">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A13, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B13">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A13, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5078,7 +5068,7 @@
         <v>102</v>
       </c>
       <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A14, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B14">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A14, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5087,7 +5077,7 @@
         <v>103</v>
       </c>
       <c r="B15" s="1" cm="1">
-        <f t="array" ref="B15">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A15, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B15">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A15, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5096,7 +5086,7 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" cm="1">
-        <f t="array" ref="B16">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A16, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B16">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A16, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5105,7 +5095,7 @@
         <v>105</v>
       </c>
       <c r="B17" s="1" cm="1">
-        <f t="array" ref="B17">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A17, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B17">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A17, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5114,7 +5104,7 @@
         <v>106</v>
       </c>
       <c r="B18" s="1" cm="1">
-        <f t="array" ref="B18">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A18, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B18">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A18, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5123,7 +5113,7 @@
         <v>107</v>
       </c>
       <c r="B19" s="1" cm="1">
-        <f t="array" ref="B19">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A19, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B19">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A19, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5132,7 +5122,7 @@
         <v>108</v>
       </c>
       <c r="B20" s="1" cm="1">
-        <f t="array" ref="B20">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A20, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B20">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A20, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5141,7 +5131,7 @@
         <v>109</v>
       </c>
       <c r="B21" s="1" cm="1">
-        <f t="array" ref="B21">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A21, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B21">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A21, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5150,7 +5140,7 @@
         <v>110</v>
       </c>
       <c r="B22" s="1" cm="1">
-        <f t="array" ref="B22">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A22, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
+        <f t="array" ref="B22">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A22, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
         <v>0</v>
       </c>
     </row>
@@ -5159,8 +5149,8 @@
         <v>111</v>
       </c>
       <c r="B23" s="1" cm="1">
-        <f t="array" ref="B23">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A23, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>2.7962691171640186E-2</v>
+        <f t="array" ref="B23">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A23, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.2715266890966266E-2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
@@ -5168,8 +5158,8 @@
         <v>112</v>
       </c>
       <c r="B24" s="1" cm="1">
-        <f t="array" ref="B24">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A24, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>6.7777492243128901E-2</v>
+        <f t="array" ref="B24">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A24, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>8.5008784462401454E-2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -5177,8 +5167,8 @@
         <v>113</v>
       </c>
       <c r="B25" s="1" cm="1">
-        <f t="array" ref="B25">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A25, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.14543881139606851</v>
+        <f t="array" ref="B25">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A25, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.15062073901751249</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
@@ -5186,8 +5176,8 @@
         <v>114</v>
       </c>
       <c r="B26" s="1" cm="1">
-        <f t="array" ref="B26">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A26, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.23904628048718468</v>
+        <f t="array" ref="B26">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A26, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.19761554699401707</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -5195,8 +5185,8 @@
         <v>115</v>
       </c>
       <c r="B27" s="1" cm="1">
-        <f t="array" ref="B27">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A27, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.30659956296545854</v>
+        <f t="array" ref="B27">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A27, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.28632755292985834</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -5204,8 +5194,8 @@
         <v>116</v>
       </c>
       <c r="B28" s="1" cm="1">
-        <f t="array" ref="B28">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A28, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.40888188953313342</v>
+        <f t="array" ref="B28">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A28, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.37961928114562227</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -5213,8 +5203,8 @@
         <v>117</v>
       </c>
       <c r="B29" s="1" cm="1">
-        <f t="array" ref="B29">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A29, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.52739383298460396</v>
+        <f t="array" ref="B29">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A29, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.48552236378629043</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -5222,8 +5212,8 @@
         <v>118</v>
       </c>
       <c r="B30" s="1" cm="1">
-        <f t="array" ref="B30">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A30, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.64381212836634294</v>
+        <f t="array" ref="B30">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A30, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.61975345060986164</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -5231,8 +5221,8 @@
         <v>119</v>
       </c>
       <c r="B31" s="1" cm="1">
-        <f t="array" ref="B31">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A31, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.77595610507325929</v>
+        <f t="array" ref="B31">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A31, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.74300271195763656</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -5240,8 +5230,8 @@
         <v>120</v>
       </c>
       <c r="B32" s="1" cm="1">
-        <f t="array" ref="B32">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A32, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>0.91102014561373323</v>
+        <f t="array" ref="B32">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A32, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.86987482262286164</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -5249,8 +5239,8 @@
         <v>121</v>
       </c>
       <c r="B33" s="1" cm="1">
-        <f t="array" ref="B33">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A33, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.0374245671186078</v>
+        <f t="array" ref="B33">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A33, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.99432704623960966</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
@@ -5258,8 +5248,8 @@
         <v>122</v>
       </c>
       <c r="B34" s="1" cm="1">
-        <f t="array" ref="B34">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A34, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.1719679818243085</v>
+        <f t="array" ref="B34">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A34, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.1062289920781687</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -5267,8 +5257,8 @@
         <v>123</v>
       </c>
       <c r="B35" s="1" cm="1">
-        <f t="array" ref="B35">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A35, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.2804156906125748</v>
+        <f t="array" ref="B35">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A35, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.2216488451997378</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
@@ -5276,8 +5266,8 @@
         <v>124</v>
       </c>
       <c r="B36" s="1" cm="1">
-        <f t="array" ref="B36">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A36, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.3854052142857753</v>
+        <f t="array" ref="B36">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A36, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.3323159912990032</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -5285,8 +5275,8 @@
         <v>125</v>
       </c>
       <c r="B37" s="1" cm="1">
-        <f t="array" ref="B37">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A37, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.4883406698727892</v>
+        <f t="array" ref="B37">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A37, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.4352010028062399</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
@@ -5294,8 +5284,8 @@
         <v>126</v>
       </c>
       <c r="B38" s="1" cm="1">
-        <f t="array" ref="B38">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A38, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.5903674327693906</v>
+        <f t="array" ref="B38">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A38, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5236078466212977</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -5303,8 +5293,8 @@
         <v>127</v>
       </c>
       <c r="B39" s="1" cm="1">
-        <f t="array" ref="B39">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A39, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.6789952010944873</v>
+        <f t="array" ref="B39">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A39, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.6063523043173316</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -5312,8 +5302,8 @@
         <v>128</v>
       </c>
       <c r="B40" s="1" cm="1">
-        <f t="array" ref="B40">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A40, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.7462334310187764</v>
+        <f t="array" ref="B40">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A40, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.6765523294840019</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -5321,8 +5311,8 @@
         <v>129</v>
       </c>
       <c r="B41" s="1" cm="1">
-        <f t="array" ref="B41">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A41, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.8043124292199</v>
+        <f t="array" ref="B41">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A41, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7333905947399479</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -5330,8 +5320,8 @@
         <v>130</v>
       </c>
       <c r="B42" s="1" cm="1">
-        <f t="array" ref="B42">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A42, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10)</f>
-        <v>1.8583570568708385</v>
+        <f t="array" ref="B42">_xll.PriceButterfly('Fly Params'!$B$4, 'Fly Params'!$B$5, A42, 'Fly Params'!$B$7, 'Fly Params'!$B$8, 'Fly Params'!$B$9, 'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7842187977521906</v>
       </c>
     </row>
   </sheetData>
@@ -5360,369 +5350,369 @@
       <c r="A2" s="1">
         <v>0.1</v>
       </c>
-      <c r="B2" s="14" cm="1">
-        <f t="array" ref="B2">_xll.PriceButterfly('Fly Params'!$B$4,A2,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>4.2445489795389708</v>
+      <c r="B2" s="10" cm="1">
+        <f t="array" ref="B2">_xll.PriceButterfly('Fly Params'!$B$4,A2,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>4.1913717983835088</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.11</v>
       </c>
-      <c r="B3" s="14" cm="1">
-        <f t="array" ref="B3">_xll.PriceButterfly('Fly Params'!$B$4,A3,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.9688435128858908</v>
+      <c r="B3" s="10" cm="1">
+        <f t="array" ref="B3">_xll.PriceButterfly('Fly Params'!$B$4,A3,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.9125836781529522</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>0.12</v>
       </c>
-      <c r="B4" s="14" cm="1">
-        <f t="array" ref="B4">_xll.PriceButterfly('Fly Params'!$B$4,A4,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.7192454920194908</v>
+      <c r="B4" s="10" cm="1">
+        <f t="array" ref="B4">_xll.PriceButterfly('Fly Params'!$B$4,A4,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.6593723710410586</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>0.13</v>
       </c>
-      <c r="B5" s="14" cm="1">
-        <f t="array" ref="B5">_xll.PriceButterfly('Fly Params'!$B$4,A5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.4912475960139853</v>
+      <c r="B5" s="10" cm="1">
+        <f t="array" ref="B5">_xll.PriceButterfly('Fly Params'!$B$4,A5,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.4275314445771778</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="B6" s="14" cm="1">
-        <f t="array" ref="B6">_xll.PriceButterfly('Fly Params'!$B$4,A6,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.2802441249134953</v>
+      <c r="B6" s="10" cm="1">
+        <f t="array" ref="B6">_xll.PriceButterfly('Fly Params'!$B$4,A6,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.2121047249499206</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>0.15</v>
       </c>
-      <c r="B7" s="14" cm="1">
-        <f t="array" ref="B7">_xll.PriceButterfly('Fly Params'!$B$4,A7,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>3.0833213713433389</v>
+      <c r="B7" s="10" cm="1">
+        <f t="array" ref="B7">_xll.PriceButterfly('Fly Params'!$B$4,A7,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>3.0121315878495549</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>0.16</v>
       </c>
-      <c r="B8" s="14" cm="1">
-        <f t="array" ref="B8">_xll.PriceButterfly('Fly Params'!$B$4,A8,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.8982338587863437</v>
+      <c r="B8" s="10" cm="1">
+        <f t="array" ref="B8">_xll.PriceButterfly('Fly Params'!$B$4,A8,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.8268647789696582</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>0.17</v>
       </c>
-      <c r="B9" s="14" cm="1">
-        <f t="array" ref="B9">_xll.PriceButterfly('Fly Params'!$B$4,A9,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.7241566692795551</v>
+      <c r="B9" s="10" cm="1">
+        <f t="array" ref="B9">_xll.PriceButterfly('Fly Params'!$B$4,A9,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.6521054667032491</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>0.18</v>
       </c>
-      <c r="B10" s="14" cm="1">
-        <f t="array" ref="B10">_xll.PriceButterfly('Fly Params'!$B$4,A10,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.5636423386376928</v>
+      <c r="B10" s="10" cm="1">
+        <f t="array" ref="B10">_xll.PriceButterfly('Fly Params'!$B$4,A10,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.4879074618227905</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>0.19</v>
       </c>
-      <c r="B11" s="14" cm="1">
-        <f t="array" ref="B11">_xll.PriceButterfly('Fly Params'!$B$4,A11,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.4050048511597044</v>
+      <c r="B11" s="10" cm="1">
+        <f t="array" ref="B11">_xll.PriceButterfly('Fly Params'!$B$4,A11,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.3330734883356836</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>0.2</v>
       </c>
-      <c r="B12" s="14" cm="1">
-        <f t="array" ref="B12">_xll.PriceButterfly('Fly Params'!$B$4,A12,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.2605169715067799</v>
+      <c r="B12" s="10" cm="1">
+        <f t="array" ref="B12">_xll.PriceButterfly('Fly Params'!$B$4,A12,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.1844945065091466</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>0.21</v>
       </c>
-      <c r="B13" s="14" cm="1">
-        <f t="array" ref="B13">_xll.PriceButterfly('Fly Params'!$B$4,A13,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>2.1218130343404926</v>
+      <c r="B13" s="10" cm="1">
+        <f t="array" ref="B13">_xll.PriceButterfly('Fly Params'!$B$4,A13,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>2.0436406444439843</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>0.22</v>
       </c>
-      <c r="B14" s="14" cm="1">
-        <f t="array" ref="B14">_xll.PriceButterfly('Fly Params'!$B$4,A14,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.9806582646617201</v>
+      <c r="B14" s="10" cm="1">
+        <f t="array" ref="B14">_xll.PriceButterfly('Fly Params'!$B$4,A14,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.9104214044523147</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>0.23</v>
       </c>
-      <c r="B15" s="14" cm="1">
-        <f t="array" ref="B15">_xll.PriceButterfly('Fly Params'!$B$4,A15,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.8583570568708385</v>
+      <c r="B15" s="10" cm="1">
+        <f t="array" ref="B15">_xll.PriceButterfly('Fly Params'!$B$4,A15,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.7842187977521906</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>0.24</v>
       </c>
-      <c r="B16" s="14" cm="1">
-        <f t="array" ref="B16">_xll.PriceButterfly('Fly Params'!$B$4,A16,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.7423928408351603</v>
+      <c r="B16" s="10" cm="1">
+        <f t="array" ref="B16">_xll.PriceButterfly('Fly Params'!$B$4,A16,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.6677598548520081</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>0.25</v>
       </c>
-      <c r="B17" s="14" cm="1">
-        <f t="array" ref="B17">_xll.PriceButterfly('Fly Params'!$B$4,A17,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.63389471493233</v>
+      <c r="B17" s="10" cm="1">
+        <f t="array" ref="B17">_xll.PriceButterfly('Fly Params'!$B$4,A17,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.5610886272180231</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>0.26</v>
       </c>
-      <c r="B18" s="14" cm="1">
-        <f t="array" ref="B18">_xll.PriceButterfly('Fly Params'!$B$4,A18,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.5383738961462861</v>
+      <c r="B18" s="10" cm="1">
+        <f t="array" ref="B18">_xll.PriceButterfly('Fly Params'!$B$4,A18,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.4610674349610786</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>0.27</v>
       </c>
-      <c r="B19" s="14" cm="1">
-        <f t="array" ref="B19">_xll.PriceButterfly('Fly Params'!$B$4,A19,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.4455746876770448</v>
+      <c r="B19" s="10" cm="1">
+        <f t="array" ref="B19">_xll.PriceButterfly('Fly Params'!$B$4,A19,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.3638243572321311</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>0.28000000000000003</v>
       </c>
-      <c r="B20" s="14" cm="1">
-        <f t="array" ref="B20">_xll.PriceButterfly('Fly Params'!$B$4,A20,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.3527977916074612</v>
+      <c r="B20" s="10" cm="1">
+        <f t="array" ref="B20">_xll.PriceButterfly('Fly Params'!$B$4,A20,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.2710642558820329</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>0.28999999999999998</v>
       </c>
-      <c r="B21" s="14" cm="1">
-        <f t="array" ref="B21">_xll.PriceButterfly('Fly Params'!$B$4,A21,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.2645245399924967</v>
+      <c r="B21" s="10" cm="1">
+        <f t="array" ref="B21">_xll.PriceButterfly('Fly Params'!$B$4,A21,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.1854764273945904</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>0.3</v>
       </c>
-      <c r="B22" s="14" cm="1">
-        <f t="array" ref="B22">_xll.PriceButterfly('Fly Params'!$B$4,A22,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.1777505209969146</v>
+      <c r="B22" s="10" cm="1">
+        <f t="array" ref="B22">_xll.PriceButterfly('Fly Params'!$B$4,A22,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.1091705204489983</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>0.31</v>
       </c>
-      <c r="B23" s="14" cm="1">
-        <f t="array" ref="B23">_xll.PriceButterfly('Fly Params'!$B$4,A23,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.0977296836683994</v>
+      <c r="B23" s="10" cm="1">
+        <f t="array" ref="B23">_xll.PriceButterfly('Fly Params'!$B$4,A23,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>1.03752926171369</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>0.32</v>
       </c>
-      <c r="B24" s="14" cm="1">
-        <f t="array" ref="B24">_xll.PriceButterfly('Fly Params'!$B$4,A24,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>1.0235488612128414</v>
+      <c r="B24" s="10" cm="1">
+        <f t="array" ref="B24">_xll.PriceButterfly('Fly Params'!$B$4,A24,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.96733522089546753</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>0.33</v>
       </c>
-      <c r="B25" s="14" cm="1">
-        <f t="array" ref="B25">_xll.PriceButterfly('Fly Params'!$B$4,A25,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.95668597429344437</v>
+      <c r="B25" s="10" cm="1">
+        <f t="array" ref="B25">_xll.PriceButterfly('Fly Params'!$B$4,A25,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.89997568264630168</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>0.34</v>
       </c>
-      <c r="B26" s="14" cm="1">
-        <f t="array" ref="B26">_xll.PriceButterfly('Fly Params'!$B$4,A26,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.89632615681331451</v>
+      <c r="B26" s="10" cm="1">
+        <f t="array" ref="B26">_xll.PriceButterfly('Fly Params'!$B$4,A26,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.8383096665903782</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>0.35</v>
       </c>
-      <c r="B27" s="14" cm="1">
-        <f t="array" ref="B27">_xll.PriceButterfly('Fly Params'!$B$4,A27,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.84301463188661074</v>
+      <c r="B27" s="10" cm="1">
+        <f t="array" ref="B27">_xll.PriceButterfly('Fly Params'!$B$4,A27,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.78050128828524201</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>0.36</v>
       </c>
-      <c r="B28" s="14" cm="1">
-        <f t="array" ref="B28">_xll.PriceButterfly('Fly Params'!$B$4,A28,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.79858109091482099</v>
+      <c r="B28" s="10" cm="1">
+        <f t="array" ref="B28">_xll.PriceButterfly('Fly Params'!$B$4,A28,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.72565606895011037</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>0.37</v>
       </c>
-      <c r="B29" s="14" cm="1">
-        <f t="array" ref="B29">_xll.PriceButterfly('Fly Params'!$B$4,A29,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.75757774569119007</v>
+      <c r="B29" s="10" cm="1">
+        <f t="array" ref="B29">_xll.PriceButterfly('Fly Params'!$B$4,A29,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.67467062358963226</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>0.38</v>
       </c>
-      <c r="B30" s="14" cm="1">
-        <f t="array" ref="B30">_xll.PriceButterfly('Fly Params'!$B$4,A30,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.71314214652871044</v>
+      <c r="B30" s="10" cm="1">
+        <f t="array" ref="B30">_xll.PriceButterfly('Fly Params'!$B$4,A30,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.63146428369368657</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>0.39</v>
       </c>
-      <c r="B31" s="14" cm="1">
-        <f t="array" ref="B31">_xll.PriceButterfly('Fly Params'!$B$4,A31,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.66480853261455408</v>
+      <c r="B31" s="10" cm="1">
+        <f t="array" ref="B31">_xll.PriceButterfly('Fly Params'!$B$4,A31,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.59363613112031643</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>0.4</v>
       </c>
-      <c r="B32" s="14" cm="1">
-        <f t="array" ref="B32">_xll.PriceButterfly('Fly Params'!$B$4,A32,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.61607079502593898</v>
+      <c r="B32" s="10" cm="1">
+        <f t="array" ref="B32">_xll.PriceButterfly('Fly Params'!$B$4,A32,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.5599062172089031</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>0.41</v>
       </c>
-      <c r="B33" s="14" cm="1">
-        <f t="array" ref="B33">_xll.PriceButterfly('Fly Params'!$B$4,A33,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.57285369430810995</v>
+      <c r="B33" s="10" cm="1">
+        <f t="array" ref="B33">_xll.PriceButterfly('Fly Params'!$B$4,A33,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.52806381781686795</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>0.42</v>
       </c>
-      <c r="B34" s="14" cm="1">
-        <f t="array" ref="B34">_xll.PriceButterfly('Fly Params'!$B$4,A34,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.53927077101698728</v>
+      <c r="B34" s="10" cm="1">
+        <f t="array" ref="B34">_xll.PriceButterfly('Fly Params'!$B$4,A34,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.49608300301630237</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>0.43</v>
       </c>
-      <c r="B35" s="14" cm="1">
-        <f t="array" ref="B35">_xll.PriceButterfly('Fly Params'!$B$4,A35,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.51328378740108604</v>
+      <c r="B35" s="10" cm="1">
+        <f t="array" ref="B35">_xll.PriceButterfly('Fly Params'!$B$4,A35,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.46471500553838929</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>0.44</v>
       </c>
-      <c r="B36" s="14" cm="1">
-        <f t="array" ref="B36">_xll.PriceButterfly('Fly Params'!$B$4,A36,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.48979766948023062</v>
+      <c r="B36" s="10" cm="1">
+        <f t="array" ref="B36">_xll.PriceButterfly('Fly Params'!$B$4,A36,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.43590460968661482</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>0.45</v>
       </c>
-      <c r="B37" s="14" cm="1">
-        <f t="array" ref="B37">_xll.PriceButterfly('Fly Params'!$B$4,A37,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.46582670898617451</v>
+      <c r="B37" s="10" cm="1">
+        <f t="array" ref="B37">_xll.PriceButterfly('Fly Params'!$B$4,A37,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.41005844020134674</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>0.46</v>
       </c>
-      <c r="B38" s="14" cm="1">
-        <f t="array" ref="B38">_xll.PriceButterfly('Fly Params'!$B$4,A38,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.44074211989477519</v>
+      <c r="B38" s="10" cm="1">
+        <f t="array" ref="B38">_xll.PriceButterfly('Fly Params'!$B$4,A38,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.38719189312834423</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>0.47</v>
       </c>
-      <c r="B39" s="14" cm="1">
-        <f t="array" ref="B39">_xll.PriceButterfly('Fly Params'!$B$4,A39,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.41404347041275891</v>
+      <c r="B39" s="10" cm="1">
+        <f t="array" ref="B39">_xll.PriceButterfly('Fly Params'!$B$4,A39,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.36704488626576648</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>0.48</v>
       </c>
-      <c r="B40" s="14" cm="1">
-        <f t="array" ref="B40">_xll.PriceButterfly('Fly Params'!$B$4,A40,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.38512183991061377</v>
+      <c r="B40" s="10" cm="1">
+        <f t="array" ref="B40">_xll.PriceButterfly('Fly Params'!$B$4,A40,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.34929810662353233</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>0.49</v>
       </c>
-      <c r="B41" s="14" cm="1">
-        <f t="array" ref="B41">_xll.PriceButterfly('Fly Params'!$B$4,A41,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.35582019392578701</v>
+      <c r="B41" s="10" cm="1">
+        <f t="array" ref="B41">_xll.PriceButterfly('Fly Params'!$B$4,A41,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.33290923233184699</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>0.5</v>
       </c>
-      <c r="B42" s="14" cm="1">
-        <f t="array" ref="B42">_xll.PriceButterfly('Fly Params'!$B$4,A42,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10)</f>
-        <v>0.32770480078904463</v>
+      <c r="B42" s="10" cm="1">
+        <f t="array" ref="B42">_xll.PriceButterfly('Fly Params'!$B$4,A42,'Fly Params'!$B$6,'Fly Params'!$B$7,'Fly Params'!$B$8,'Fly Params'!$B$9,'Fly Params'!$B$10, 'Fly Params'!$B$11,'Fly Params'!$B$12)</f>
+        <v>0.31688311309744677</v>
       </c>
     </row>
   </sheetData>
